--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.03681</v>
+        <v>17.08056</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0728</v>
+        <v>16.36528</v>
       </c>
       <c r="E2" t="n">
-        <v>16.85262</v>
+        <v>16.88291</v>
       </c>
       <c r="F2" t="n">
-        <v>43.45062</v>
+        <v>43.05326</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05013</v>
+        <v>0.05138</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83348</v>
+        <v>1.84351</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.32923</v>
+        <v>16.974</v>
       </c>
       <c r="D3" t="n">
-        <v>16.93584</v>
+        <v>16.79119</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96621</v>
+        <v>16.92285</v>
       </c>
       <c r="F3" t="n">
-        <v>43.29161</v>
+        <v>42.76611</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05064</v>
+        <v>0.05035</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8289</v>
+        <v>1.85268</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.73932</v>
+        <v>16.93393</v>
       </c>
       <c r="D4" t="n">
-        <v>17.06809</v>
+        <v>16.84034</v>
       </c>
       <c r="E4" t="n">
-        <v>16.69837</v>
+        <v>16.89052</v>
       </c>
       <c r="F4" t="n">
-        <v>42.14881</v>
+        <v>42.64144</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05015</v>
+        <v>0.0524</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81141</v>
+        <v>1.87843</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.18153</v>
+        <v>17.13981</v>
       </c>
       <c r="D6" t="n">
-        <v>15.96878</v>
+        <v>15.89245</v>
       </c>
       <c r="E6" t="n">
-        <v>16.65329</v>
+        <v>16.55634</v>
       </c>
       <c r="F6" t="n">
-        <v>21.83634</v>
+        <v>22.13337</v>
       </c>
       <c r="G6" t="n">
-        <v>34.83991</v>
+        <v>34.64074</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83946</v>
+        <v>16.61937</v>
       </c>
       <c r="D7" t="n">
-        <v>16.16359</v>
+        <v>15.99841</v>
       </c>
       <c r="E7" t="n">
-        <v>16.58973</v>
+        <v>16.5101</v>
       </c>
       <c r="F7" t="n">
-        <v>21.96785</v>
+        <v>21.97769</v>
       </c>
       <c r="G7" t="n">
-        <v>34.45086</v>
+        <v>34.66735</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.0866</v>
+        <v>17.56787</v>
       </c>
       <c r="D8" t="n">
-        <v>15.65097</v>
+        <v>16.02729</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44672</v>
+        <v>16.42513</v>
       </c>
       <c r="F8" t="n">
-        <v>22.27529</v>
+        <v>21.72166</v>
       </c>
       <c r="G8" t="n">
-        <v>34.29914</v>
+        <v>34.81927</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61033</v>
+        <v>0.60773</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11114</v>
+        <v>1.13713</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6045</v>
+        <v>0.61663</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13327</v>
+        <v>1.13926</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.615</v>
+        <v>0.60709</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10043</v>
+        <v>1.13562</v>
       </c>
     </row>
   </sheetData>
